--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/1mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/1mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.65436560185</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>265.5869947430142</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>249.2676644073272</v>
+        <v>0.259424052</v>
+      </c>
+      <c r="Y2">
+        <v>0.263533888</v>
+      </c>
+      <c r="Z2">
+        <v>0.3697985247137896</v>
+      </c>
+      <c r="AA2">
+        <v>2.054918000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.1802354298563897</v>
+      </c>
+      <c r="AC2">
+        <v>47.86818616177387</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.65448134259</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>257.0658877723649</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>252.6399598062201</v>
+      </c>
+      <c r="X3">
+        <v>0.259524932</v>
+      </c>
+      <c r="Y3">
+        <v>0.263553948</v>
+      </c>
+      <c r="Z3">
+        <v>0.3698835949808957</v>
+      </c>
+      <c r="AA3">
+        <v>2.014507999999999</v>
+      </c>
+      <c r="AB3">
+        <v>0.1838820061816839</v>
+      </c>
+      <c r="AC3">
+        <v>47.26979116445806</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.65459766204</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>259.4873399417394</v>
       </c>
-      <c r="V4">
-        <v>4.390870895174299</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.259580304</v>
+      </c>
+      <c r="Y4">
+        <v>0.263571778</v>
+      </c>
+      <c r="Z4">
+        <v>0.3699351515912129</v>
+      </c>
+      <c r="AA4">
+        <v>1.995736999999998</v>
+      </c>
+      <c r="AB4">
+        <v>0.1856322218258762</v>
+      </c>
+      <c r="AC4">
+        <v>48.16921144907153</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.65471398148</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>251.9706979150528</v>
       </c>
-      <c r="V5">
-        <v>3.836758563509399</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>47.70496650794461</v>
+      </c>
+      <c r="X5">
+        <v>0.259634404</v>
+      </c>
+      <c r="Y5">
+        <v>0.26359311</v>
+      </c>
+      <c r="Z5">
+        <v>0.3699883124909587</v>
+      </c>
+      <c r="AA5">
+        <v>1.979352999999996</v>
+      </c>
+      <c r="AB5">
+        <v>0.1871911622328162</v>
+      </c>
+      <c r="AC5">
+        <v>47.16668779133258</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.65482972223</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>255.7332963503088</v>
       </c>
-      <c r="V6">
-        <v>3.758321824713433</v>
-      </c>
-      <c r="W6" t="b">
-        <v>0</v>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.259671956</v>
+      </c>
+      <c r="Y6">
+        <v>0.263609666</v>
+      </c>
+      <c r="Z6">
+        <v>0.370026459515394</v>
+      </c>
+      <c r="AA6">
+        <v>1.968855000000005</v>
+      </c>
+      <c r="AB6">
+        <v>0.1882057786539138</v>
+      </c>
+      <c r="AC6">
+        <v>48.13048416734195</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.65494546296</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>251.2802410014063</v>
       </c>
-      <c r="V7">
-        <v>2.396649733655345</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.259701552</v>
+      </c>
+      <c r="Y7">
+        <v>0.263621128</v>
+      </c>
+      <c r="Z7">
+        <v>0.3700553948251546</v>
+      </c>
+      <c r="AA7">
+        <v>1.959787999999996</v>
+      </c>
+      <c r="AB7">
+        <v>0.1890888078755709</v>
+      </c>
+      <c r="AC7">
+        <v>47.51428121364206</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.65506178241</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>250.9613287119048</v>
       </c>
-      <c r="V8">
-        <v>2.667804407209498</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.259727966</v>
+      </c>
+      <c r="Y8">
+        <v>0.26363896</v>
+      </c>
+      <c r="Z8">
+        <v>0.3700866351982718</v>
+      </c>
+      <c r="AA8">
+        <v>1.955497000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.1895185247699127</v>
+      </c>
+      <c r="AC8">
+        <v>47.56182079177733</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.65517752315</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>251.5109660547562</v>
       </c>
-      <c r="V9">
-        <v>0.2759952618229485</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.259751834</v>
+      </c>
+      <c r="Y9">
+        <v>0.263656152</v>
+      </c>
+      <c r="Z9">
+        <v>0.3701156329497725</v>
+      </c>
+      <c r="AA9">
+        <v>1.952159000000002</v>
+      </c>
+      <c r="AB9">
+        <v>0.189856514926434</v>
+      </c>
+      <c r="AC9">
+        <v>47.75099548093664</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.6552938426</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>251.3266709264423</v>
       </c>
-      <c r="V10">
-        <v>0.2797441797718465</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.259780794</v>
+      </c>
+      <c r="Y10">
+        <v>0.26367271</v>
+      </c>
+      <c r="Z10">
+        <v>0.3701477528366403</v>
+      </c>
+      <c r="AA10">
+        <v>1.945957999999997</v>
+      </c>
+      <c r="AB10">
+        <v>0.1904763201117063</v>
+      </c>
+      <c r="AC10">
+        <v>47.87177942399449</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.65540958333</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>246.9508759035051</v>
       </c>
-      <c r="V11">
-        <v>2.581213182614468</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.259807844</v>
+      </c>
+      <c r="Y11">
+        <v>0.263685446</v>
+      </c>
+      <c r="Z11">
+        <v>0.3701758099013862</v>
+      </c>
+      <c r="AA11">
+        <v>1.938800999999998</v>
+      </c>
+      <c r="AB11">
+        <v>0.1911919722852329</v>
+      </c>
+      <c r="AC11">
+        <v>47.21502502155693</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.65552590278</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>249.9757106566897</v>
       </c>
-      <c r="V12">
-        <v>2.240621231462457</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.259832668</v>
+      </c>
+      <c r="Y12">
+        <v>0.263697544</v>
+      </c>
+      <c r="Z12">
+        <v>0.370201850443282</v>
+      </c>
+      <c r="AA12">
+        <v>1.932437999999998</v>
+      </c>
+      <c r="AB12">
+        <v>0.1918332539364742</v>
+      </c>
+      <c r="AC12">
+        <v>47.95365398035536</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.65564164352</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>249.9174700833418</v>
       </c>
-      <c r="V13">
-        <v>1.729821680419413</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.25984508</v>
+      </c>
+      <c r="Y13">
+        <v>0.26370264</v>
+      </c>
+      <c r="Z13">
+        <v>0.3702141919796917</v>
+      </c>
+      <c r="AA13">
+        <v>1.928780000000003</v>
+      </c>
+      <c r="AB13">
+        <v>0.1922024747905456</v>
+      </c>
+      <c r="AC13">
+        <v>48.03475624341043</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.65575796297</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>244.8301076918591</v>
       </c>
-      <c r="V14">
-        <v>2.954146180605718</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.259845716</v>
+      </c>
+      <c r="Y14">
+        <v>0.263700092</v>
+      </c>
+      <c r="Z14">
+        <v>0.3702128234466779</v>
+      </c>
+      <c r="AA14">
+        <v>1.927188000000001</v>
+      </c>
+      <c r="AB14">
+        <v>0.1923601094920224</v>
+      </c>
+      <c r="AC14">
+        <v>47.09554632254967</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.65587428241</v>
       </c>
@@ -1482,11 +1728,26 @@
       <c r="U15">
         <v>250.3618495346964</v>
       </c>
-      <c r="V15">
-        <v>3.073513109750532</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.25985208</v>
+      </c>
+      <c r="Y15">
+        <v>0.263697864</v>
+      </c>
+      <c r="Z15">
+        <v>0.3702157032845702</v>
+      </c>
+      <c r="AA15">
+        <v>1.922891999999997</v>
+      </c>
+      <c r="AB15">
+        <v>0.1927902034144962</v>
+      </c>
+      <c r="AC15">
+        <v>48.26731189902362</v>
       </c>
     </row>
   </sheetData>
